--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:47:57+00:00</t>
+    <t>2024-11-12T08:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:54:48+00:00</t>
+    <t>2024-11-12T10:30:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T10:30:22+00:00</t>
+    <t>2024-11-12T12:40:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T12:40:22+00:00</t>
+    <t>2024-11-12T14:33:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:33:00+00:00</t>
+    <t>2024-11-12T14:36:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:36:04+00:00</t>
+    <t>2024-11-12T18:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:20:22+00:00</t>
+    <t>2024-11-12T18:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$83</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3090" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3205" uniqueCount="525">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:30:34+00:00</t>
+    <t>2024-11-12T19:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -520,6 +520,15 @@
     <t>C.32, C.33, C.39</t>
   </si>
   <si>
+    <t>Coverage.identifier:VDASID</t>
+  </si>
+  <si>
+    <t>VDASID</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:VDASID.id</t>
+  </si>
+  <si>
     <t>Coverage.identifier.id</t>
   </si>
   <si>
@@ -539,6 +548,9 @@
     <t>n/a</t>
   </si>
   <si>
+    <t>Coverage.identifier:VDASID.extension</t>
+  </si>
+  <si>
     <t>Coverage.identifier.extension</t>
   </si>
   <si>
@@ -555,6 +567,9 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>Coverage.identifier:VDASID.use</t>
+  </si>
+  <si>
     <t>Coverage.identifier.use</t>
   </si>
   <si>
@@ -580,6 +595,9 @@
   </si>
   <si>
     <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:VDASID.type</t>
   </si>
   <si>
     <t>Coverage.identifier.type</t>
@@ -616,6 +634,9 @@
     <t>CX.5</t>
   </si>
   <si>
+    <t>Coverage.identifier:VDASID.system</t>
+  </si>
+  <si>
     <t>Coverage.identifier.system</t>
   </si>
   <si>
@@ -644,6 +665,9 @@
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:VDASID.value</t>
   </si>
   <si>
     <t>Coverage.identifier.value</t>
@@ -678,6 +702,9 @@
     <t>CX.1 / EI.1</t>
   </si>
   <si>
+    <t>Coverage.identifier:VDASID.period</t>
+  </si>
+  <si>
     <t>Coverage.identifier.period</t>
   </si>
   <si>
@@ -700,65 +727,34 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
+    <t>Coverage.identifier:VDASID.assigner</t>
+  </si>
+  <si>
     <t>Coverage.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:VDASID</t>
-  </si>
-  <si>
-    <t>VDASID</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:VDASID.id</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:VDASID.extension</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:VDASID.use</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:VDASID.type</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:VDASID.system</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:VDASID.value</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:VDASID.period</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:VDASID.assigner</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-organization)
 </t>
   </si>
   <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
     <t>Coverage.status</t>
   </si>
   <si>
@@ -1156,6 +1152,222 @@
     <t>http://svc.co.at/CodeSystem/ecard-versichertenkategorie-cs</t>
   </si>
   <si>
+    <t>Coverage.class:Versichertenkategorien.type.id</t>
+  </si>
+  <si>
+    <t>Coverage.class.type.id</t>
+  </si>
+  <si>
+    <t>Coverage.class:Versichertenkategorien.type.extension</t>
+  </si>
+  <si>
+    <t>Coverage.class.type.extension</t>
+  </si>
+  <si>
+    <t>Coverage.class:Versichertenkategorien.type.coding</t>
+  </si>
+  <si>
+    <t>Coverage.class.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Coverage.class:Versichertenkategorien.type.coding.id</t>
+  </si>
+  <si>
+    <t>Coverage.class.type.coding.id</t>
+  </si>
+  <si>
+    <t>Coverage.class:Versichertenkategorien.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Coverage.class.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Coverage.class:Versichertenkategorien.type.coding.system</t>
+  </si>
+  <si>
+    <t>Coverage.class.type.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should be an absolute reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>Coverage.class:Versichertenkategorien.type.coding.version</t>
+  </si>
+  <si>
+    <t>Coverage.class.type.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>Coverage.class:Versichertenkategorien.type.coding.code</t>
+  </si>
+  <si>
+    <t>Coverage.class.type.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cod-1
+</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>Coverage.class:Versichertenkategorien.type.coding.display</t>
+  </si>
+  <si>
+    <t>Coverage.class.type.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>Coverage.class:Versichertenkategorien.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Coverage.class.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>Coverage.class:Versichertenkategorien.type.text</t>
+  </si>
+  <si>
+    <t>Coverage.class.type.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
     <t>Coverage.class:Versichertenkategorien.value</t>
   </si>
   <si>
@@ -1373,10 +1585,6 @@
   </si>
   <si>
     <t>Coverage.subrogation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
   </si>
   <si>
     <t>Reimbursement to insurer</t>
@@ -1738,10 +1946,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP80"/>
+  <dimension ref="A1:AP83"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="54.30859375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="61.02734375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="53.57421875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.57421875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -3117,9 +3325,11 @@
         <v>161</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>19</v>
       </c>
@@ -3137,19 +3347,23 @@
         <v>19</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>91</v>
+        <v>149</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O12" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>19</v>
       </c>
@@ -3197,34 +3411,34 @@
         <v>19</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>165</v>
+        <v>19</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>19</v>
+        <v>156</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>19</v>
+        <v>160</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>19</v>
@@ -3232,21 +3446,21 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>19</v>
@@ -3258,17 +3472,15 @@
         <v>19</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>19</v>
@@ -3305,40 +3517,40 @@
         <v>19</v>
       </c>
       <c r="AB13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>19</v>
@@ -3352,46 +3564,44 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>19</v>
+        <v>136</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>19</v>
       </c>
@@ -3415,43 +3625,43 @@
         <v>19</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>178</v>
+        <v>19</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>19</v>
+        <v>173</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>19</v>
+        <v>174</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>19</v>
@@ -3460,7 +3670,7 @@
         <v>19</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>19</v>
@@ -3469,15 +3679,15 @@
         <v>19</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>134</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3494,25 +3704,25 @@
         <v>19</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>182</v>
+        <v>109</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>19</v>
@@ -3537,13 +3747,13 @@
         <v>19</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>187</v>
+        <v>113</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>19</v>
@@ -3561,7 +3771,7 @@
         <v>19</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3582,7 +3792,7 @@
         <v>19</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>19</v>
@@ -3591,15 +3801,15 @@
         <v>19</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>191</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3622,19 +3832,19 @@
         <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>103</v>
+        <v>188</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>19</v>
@@ -3644,10 +3854,10 @@
         <v>19</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>197</v>
+        <v>19</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>198</v>
+        <v>19</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>19</v>
@@ -3659,13 +3869,13 @@
         <v>19</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>19</v>
+        <v>194</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>19</v>
+        <v>195</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>19</v>
@@ -3683,7 +3893,7 @@
         <v>19</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3704,7 +3914,7 @@
         <v>19</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>19</v>
@@ -3713,15 +3923,15 @@
         <v>19</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3729,7 +3939,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>89</v>
@@ -3744,18 +3954,20 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L17" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>19</v>
       </c>
@@ -3764,10 +3976,10 @@
         <v>19</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>19</v>
+        <v>204</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>19</v>
@@ -3803,7 +4015,7 @@
         <v>19</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3812,7 +4024,7 @@
         <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>209</v>
+        <v>19</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>101</v>
@@ -3824,7 +4036,7 @@
         <v>19</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>19</v>
@@ -3833,15 +4045,15 @@
         <v>19</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3864,15 +4076,17 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>19</v>
@@ -3885,7 +4099,7 @@
         <v>19</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>19</v>
+        <v>215</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>19</v>
@@ -3930,7 +4144,7 @@
         <v>89</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>19</v>
+        <v>217</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>101</v>
@@ -3942,7 +4156,7 @@
         <v>19</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>19</v>
@@ -3951,15 +4165,15 @@
         <v>19</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3982,17 +4196,15 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>19</v>
@@ -4041,7 +4253,7 @@
         <v>19</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4062,7 +4274,7 @@
         <v>19</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>19</v>
@@ -4071,19 +4283,17 @@
         <v>19</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>19</v>
       </c>
@@ -4104,20 +4314,18 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>149</v>
+        <v>230</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>150</v>
+        <v>231</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>151</v>
+        <v>232</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>19</v>
       </c>
@@ -4165,13 +4373,13 @@
         <v>19</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>19</v>
@@ -4180,30 +4388,30 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>158</v>
+        <v>235</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>159</v>
+        <v>19</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>160</v>
+        <v>19</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>19</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>161</v>
+        <v>237</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4211,7 +4419,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>89</v>
@@ -4220,22 +4428,26 @@
         <v>19</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>162</v>
+        <v>238</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>19</v>
       </c>
@@ -4259,13 +4471,13 @@
         <v>19</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>19</v>
+        <v>242</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>19</v>
+        <v>243</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>19</v>
@@ -4283,28 +4495,28 @@
         <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>164</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>165</v>
+        <v>19</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>19</v>
+        <v>245</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>166</v>
+        <v>246</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>19</v>
@@ -4318,21 +4530,21 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>167</v>
+        <v>247</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>19</v>
@@ -4341,21 +4553,21 @@
         <v>19</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>138</v>
+        <v>248</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>19</v>
       </c>
@@ -4379,43 +4591,41 @@
         <v>19</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>19</v>
+        <v>251</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>169</v>
+        <v>19</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>170</v>
+        <v>19</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>171</v>
+        <v>247</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>19</v>
@@ -4424,7 +4634,7 @@
         <v>19</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>166</v>
+        <v>19</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>19</v>
@@ -4438,10 +4648,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>172</v>
+        <v>252</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4452,32 +4662,28 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>109</v>
+        <v>253</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>173</v>
+        <v>254</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>19</v>
       </c>
@@ -4501,13 +4707,13 @@
         <v>19</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>178</v>
+        <v>19</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>19</v>
@@ -4525,13 +4731,13 @@
         <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>179</v>
+        <v>252</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>19</v>
@@ -4546,7 +4752,7 @@
         <v>19</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>19</v>
@@ -4555,15 +4761,15 @@
         <v>19</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>134</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4583,23 +4789,19 @@
         <v>19</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>19</v>
       </c>
@@ -4623,13 +4825,13 @@
         <v>19</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>187</v>
+        <v>19</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>188</v>
+        <v>19</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>189</v>
+        <v>19</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>19</v>
@@ -4647,7 +4849,7 @@
         <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4656,10 +4858,10 @@
         <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>19</v>
@@ -4668,7 +4870,7 @@
         <v>19</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>19</v>
@@ -4677,26 +4879,26 @@
         <v>19</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>192</v>
+        <v>257</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>19</v>
+        <v>136</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>19</v>
@@ -4705,23 +4907,21 @@
         <v>19</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>193</v>
+        <v>138</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>19</v>
       </c>
@@ -4733,7 +4933,7 @@
         <v>19</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>198</v>
+        <v>19</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>19</v>
@@ -4769,19 +4969,19 @@
         <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>19</v>
@@ -4790,7 +4990,7 @@
         <v>19</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>19</v>
@@ -4799,49 +4999,51 @@
         <v>19</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>201</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>202</v>
+        <v>258</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>19</v>
+        <v>259</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>203</v>
+        <v>137</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>204</v>
+        <v>260</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>205</v>
+        <v>261</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>19</v>
       </c>
@@ -4853,7 +5055,7 @@
         <v>19</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>207</v>
+        <v>19</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>19</v>
@@ -4889,19 +5091,19 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>208</v>
+        <v>262</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>209</v>
+        <v>19</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>19</v>
@@ -4910,7 +5112,7 @@
         <v>19</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>210</v>
+        <v>134</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>19</v>
@@ -4919,15 +5121,15 @@
         <v>19</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>211</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4935,7 +5137,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>89</v>
@@ -4950,13 +5152,13 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>214</v>
+        <v>264</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>215</v>
+        <v>265</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5007,10 +5209,10 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>216</v>
+        <v>263</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>89</v>
@@ -5028,7 +5230,7 @@
         <v>19</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>217</v>
+        <v>19</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>19</v>
@@ -5037,15 +5239,15 @@
         <v>19</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>218</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>219</v>
+        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5068,17 +5270,15 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>221</v>
+        <v>267</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>19</v>
@@ -5127,7 +5327,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>224</v>
+        <v>266</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5148,7 +5348,7 @@
         <v>19</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>225</v>
+        <v>19</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>19</v>
@@ -5157,15 +5357,15 @@
         <v>19</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>226</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5173,7 +5373,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>89</v>
@@ -5182,25 +5382,23 @@
         <v>19</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>109</v>
+        <v>188</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>19</v>
@@ -5225,13 +5423,13 @@
         <v>19</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>113</v>
+        <v>273</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>244</v>
+        <v>275</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>19</v>
@@ -5249,10 +5447,10 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>89</v>
@@ -5264,13 +5462,13 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>245</v>
+        <v>19</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>247</v>
+        <v>19</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>19</v>
@@ -5279,15 +5477,15 @@
         <v>19</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>19</v>
+        <v>277</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5295,7 +5493,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>89</v>
@@ -5310,17 +5508,19 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>109</v>
+        <v>279</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>249</v>
+        <v>280</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="O30" t="s" s="2">
-        <v>251</v>
+        <v>283</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>19</v>
@@ -5345,11 +5545,13 @@
         <v>19</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>252</v>
+        <v>19</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>19</v>
@@ -5367,10 +5569,10 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>89</v>
@@ -5385,27 +5587,27 @@
         <v>19</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>19</v>
+        <v>284</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>19</v>
+        <v>286</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>19</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>253</v>
+        <v>288</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>253</v>
+        <v>288</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5416,7 +5618,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>19</v>
@@ -5425,19 +5627,23 @@
         <v>19</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>254</v>
+        <v>289</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>255</v>
+        <v>290</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>19</v>
       </c>
@@ -5485,13 +5691,13 @@
         <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>253</v>
+        <v>288</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>19</v>
@@ -5503,27 +5709,27 @@
         <v>19</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>19</v>
+        <v>284</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>19</v>
+        <v>286</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>19</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>257</v>
+        <v>294</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>257</v>
+        <v>294</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5534,7 +5740,7 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>19</v>
@@ -5543,19 +5749,21 @@
         <v>19</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>203</v>
+        <v>149</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>162</v>
+        <v>295</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>163</v>
+        <v>296</v>
       </c>
       <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+      <c r="O32" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>19</v>
       </c>
@@ -5603,56 +5811,56 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>164</v>
+        <v>294</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>165</v>
+        <v>19</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>19</v>
+        <v>284</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>166</v>
+        <v>19</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>19</v>
+        <v>286</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>19</v>
+        <v>287</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>258</v>
+        <v>298</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>258</v>
+        <v>298</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>19</v>
@@ -5661,21 +5869,21 @@
         <v>19</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>137</v>
+        <v>299</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>138</v>
+        <v>300</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>19</v>
       </c>
@@ -5723,80 +5931,80 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>171</v>
+        <v>298</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>19</v>
+        <v>303</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>19</v>
+        <v>284</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>166</v>
+        <v>19</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>19</v>
+        <v>286</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>19</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>259</v>
+        <v>304</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>259</v>
+        <v>304</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>260</v>
+        <v>19</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>261</v>
+        <v>305</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>262</v>
+        <v>306</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>140</v>
+        <v>307</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>146</v>
+        <v>308</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>19</v>
@@ -5845,19 +6053,19 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>263</v>
+        <v>304</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>19</v>
@@ -5866,24 +6074,24 @@
         <v>19</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>19</v>
+        <v>309</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>19</v>
+        <v>310</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>264</v>
+        <v>311</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>264</v>
+        <v>311</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5891,7 +6099,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>89</v>
@@ -5903,19 +6111,23 @@
         <v>19</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>237</v>
+        <v>188</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>265</v>
+        <v>312</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>19</v>
       </c>
@@ -5939,13 +6151,13 @@
         <v>19</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>19</v>
+        <v>316</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>19</v>
+        <v>317</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>19</v>
@@ -5963,10 +6175,10 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>264</v>
+        <v>311</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>89</v>
@@ -5987,7 +6199,7 @@
         <v>19</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>19</v>
+        <v>318</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>19</v>
@@ -5998,10 +6210,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>267</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>267</v>
+        <v>319</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6024,16 +6236,18 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>268</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>269</v>
+        <v>321</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>19</v>
       </c>
@@ -6081,7 +6295,7 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>267</v>
+        <v>319</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6096,13 +6310,13 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>19</v>
+        <v>323</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>19</v>
+        <v>324</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>19</v>
+        <v>325</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>19</v>
@@ -6111,15 +6325,15 @@
         <v>19</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>19</v>
+        <v>326</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>270</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>270</v>
+        <v>327</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6142,17 +6356,19 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>182</v>
+        <v>230</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>271</v>
+        <v>328</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="O37" t="s" s="2">
-        <v>273</v>
+        <v>331</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>19</v>
@@ -6177,13 +6393,13 @@
         <v>19</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>275</v>
+        <v>19</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>276</v>
+        <v>19</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>19</v>
@@ -6201,7 +6417,7 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>270</v>
+        <v>327</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6219,7 +6435,7 @@
         <v>19</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>277</v>
+        <v>19</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>19</v>
@@ -6231,15 +6447,15 @@
         <v>19</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>278</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6250,7 +6466,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>19</v>
@@ -6259,22 +6475,22 @@
         <v>19</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>281</v>
+        <v>333</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>282</v>
+        <v>334</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>283</v>
+        <v>335</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>284</v>
+        <v>336</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>19</v>
@@ -6311,25 +6527,23 @@
         <v>19</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="AC38" s="2"/>
       <c r="AD38" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>19</v>
@@ -6341,27 +6555,27 @@
         <v>19</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>285</v>
+        <v>19</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>286</v>
+        <v>19</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>287</v>
+        <v>19</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>288</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>289</v>
+        <v>338</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>289</v>
+        <v>338</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6381,23 +6595,19 @@
         <v>19</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>290</v>
+        <v>211</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>291</v>
+        <v>165</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>19</v>
       </c>
@@ -6445,7 +6655,7 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>289</v>
+        <v>167</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6454,40 +6664,40 @@
         <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>285</v>
+        <v>19</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>286</v>
+        <v>19</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>287</v>
+        <v>19</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>288</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>295</v>
+        <v>339</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>295</v>
+        <v>339</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>19</v>
+        <v>136</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6503,21 +6713,21 @@
         <v>19</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>296</v>
+        <v>138</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>19</v>
       </c>
@@ -6565,7 +6775,7 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>295</v>
+        <v>175</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6577,66 +6787,68 @@
         <v>19</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>285</v>
+        <v>19</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>286</v>
+        <v>19</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>287</v>
+        <v>19</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>288</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>299</v>
+        <v>340</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>299</v>
+        <v>340</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>19</v>
+        <v>259</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>300</v>
+        <v>137</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>301</v>
+        <v>260</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O41" t="s" s="2">
-        <v>303</v>
+        <v>146</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>19</v>
@@ -6685,45 +6897,45 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>299</v>
+        <v>262</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>304</v>
+        <v>19</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>285</v>
+        <v>19</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>286</v>
+        <v>19</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>287</v>
+        <v>19</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>288</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6731,7 +6943,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>89</v>
@@ -6746,19 +6958,17 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>309</v>
+        <v>344</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>19</v>
@@ -6783,13 +6993,13 @@
         <v>19</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>19</v>
+        <v>345</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>19</v>
+        <v>346</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>19</v>
@@ -6807,10 +7017,10 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>89</v>
@@ -6831,21 +7041,21 @@
         <v>19</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>310</v>
+        <v>19</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>311</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>312</v>
+        <v>347</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>312</v>
+        <v>347</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6853,7 +7063,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
@@ -6865,22 +7075,22 @@
         <v>19</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>182</v>
+        <v>149</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>313</v>
+        <v>348</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>314</v>
+        <v>349</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>315</v>
+        <v>350</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>316</v>
+        <v>351</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>19</v>
@@ -6905,13 +7115,13 @@
         <v>19</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>187</v>
+        <v>19</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>317</v>
+        <v>19</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>318</v>
+        <v>19</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>19</v>
@@ -6929,10 +7139,10 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>312</v>
+        <v>347</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>89</v>
@@ -6953,21 +7163,21 @@
         <v>19</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>319</v>
+        <v>352</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>19</v>
+        <v>353</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>19</v>
+        <v>354</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>320</v>
+        <v>355</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>320</v>
+        <v>355</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6990,17 +7200,17 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>321</v>
+        <v>356</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>322</v>
+        <v>357</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>323</v>
+        <v>358</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>19</v>
@@ -7049,7 +7259,7 @@
         <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>320</v>
+        <v>355</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7064,32 +7274,34 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>324</v>
+        <v>19</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>325</v>
+        <v>19</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>326</v>
+        <v>19</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>19</v>
+        <v>352</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>19</v>
+        <v>353</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>327</v>
+        <v>359</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="D45" t="s" s="2">
         <v>19</v>
       </c>
@@ -7101,28 +7313,28 @@
         <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>329</v>
+        <v>361</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>19</v>
@@ -7171,13 +7383,13 @@
         <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>19</v>
@@ -7206,10 +7418,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7220,7 +7432,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>19</v>
@@ -7232,20 +7444,16 @@
         <v>19</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>334</v>
+        <v>165</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>19</v>
       </c>
@@ -7281,29 +7489,31 @@
         <v>19</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AC46" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD46" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>333</v>
+        <v>167</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>19</v>
@@ -7312,7 +7522,7 @@
         <v>19</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>19</v>
@@ -7326,21 +7536,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>339</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>19</v>
+        <v>136</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>19</v>
@@ -7352,15 +7562,17 @@
         <v>19</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>203</v>
+        <v>137</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>19</v>
@@ -7409,19 +7621,19 @@
         <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>165</v>
+        <v>19</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>19</v>
@@ -7430,7 +7642,7 @@
         <v>19</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>19</v>
@@ -7444,14 +7656,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>340</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>136</v>
+        <v>259</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7464,24 +7676,26 @@
         <v>19</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>138</v>
+        <v>260</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>168</v>
+        <v>261</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>19</v>
       </c>
@@ -7529,7 +7743,7 @@
         <v>19</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>171</v>
+        <v>262</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7550,7 +7764,7 @@
         <v>19</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>19</v>
@@ -7564,45 +7778,43 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>341</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>260</v>
+        <v>19</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>261</v>
+        <v>342</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>146</v>
+        <v>344</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>19</v>
@@ -7627,13 +7839,11 @@
         <v>19</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>19</v>
+        <v>366</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>19</v>
@@ -7651,19 +7861,19 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>263</v>
+        <v>341</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>19</v>
@@ -7672,7 +7882,7 @@
         <v>19</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>19</v>
@@ -7686,10 +7896,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7697,7 +7907,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>89</v>
@@ -7709,21 +7919,19 @@
         <v>19</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>343</v>
+        <v>165</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>344</v>
+        <v>166</v>
       </c>
       <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>345</v>
-      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>19</v>
       </c>
@@ -7747,13 +7955,13 @@
         <v>19</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>187</v>
+        <v>19</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>346</v>
+        <v>19</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>347</v>
+        <v>19</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>19</v>
@@ -7771,19 +7979,19 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>342</v>
+        <v>167</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>19</v>
@@ -7792,7 +8000,7 @@
         <v>19</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>19</v>
@@ -7806,21 +8014,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>19</v>
+        <v>136</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>19</v>
@@ -7829,23 +8037,21 @@
         <v>19</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>349</v>
+        <v>138</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>350</v>
+        <v>172</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>19</v>
       </c>
@@ -7881,31 +8087,31 @@
         <v>19</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>19</v>
+        <v>173</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>19</v>
+        <v>174</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>348</v>
+        <v>175</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>19</v>
@@ -7914,24 +8120,24 @@
         <v>19</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>353</v>
+        <v>19</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>354</v>
+        <v>19</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>355</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7942,7 +8148,7 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>19</v>
@@ -7954,17 +8160,19 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>203</v>
+        <v>373</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="O52" t="s" s="2">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>19</v>
@@ -8013,13 +8221,13 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>19</v>
@@ -8034,28 +8242,26 @@
         <v>19</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>19</v>
+        <v>379</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>353</v>
+        <v>19</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>354</v>
+        <v>19</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>360</v>
+        <v>380</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>19</v>
       </c>
@@ -8067,7 +8273,7 @@
         <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>19</v>
@@ -8076,20 +8282,16 @@
         <v>19</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>254</v>
+        <v>91</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>362</v>
+        <v>165</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>19</v>
       </c>
@@ -8137,19 +8339,19 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>333</v>
+        <v>167</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>19</v>
@@ -8158,7 +8360,7 @@
         <v>19</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>19</v>
@@ -8172,21 +8374,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>339</v>
+        <v>384</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>19</v>
+        <v>136</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>19</v>
@@ -8198,15 +8400,17 @@
         <v>19</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>203</v>
+        <v>137</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>19</v>
@@ -8243,31 +8447,31 @@
         <v>19</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>19</v>
+        <v>173</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>19</v>
+        <v>174</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>165</v>
+        <v>19</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>19</v>
@@ -8276,7 +8480,7 @@
         <v>19</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>19</v>
@@ -8290,21 +8494,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>340</v>
+        <v>386</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>19</v>
@@ -8313,21 +8517,23 @@
         <v>19</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>138</v>
+        <v>387</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>168</v>
+        <v>388</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>19</v>
       </c>
@@ -8336,7 +8542,7 @@
         <v>19</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>19</v>
+        <v>366</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>19</v>
@@ -8375,19 +8581,19 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>171</v>
+        <v>391</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>19</v>
@@ -8396,7 +8602,7 @@
         <v>19</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>166</v>
+        <v>392</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>19</v>
@@ -8405,51 +8611,49 @@
         <v>19</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>19</v>
+        <v>393</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>365</v>
+        <v>394</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>341</v>
+        <v>395</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>260</v>
+        <v>19</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>261</v>
+        <v>396</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>262</v>
+        <v>397</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>19</v>
       </c>
@@ -8497,19 +8701,19 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>263</v>
+        <v>399</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>19</v>
@@ -8518,7 +8722,7 @@
         <v>19</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>134</v>
+        <v>400</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>19</v>
@@ -8527,15 +8731,15 @@
         <v>19</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>19</v>
+        <v>401</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>366</v>
+        <v>402</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>342</v>
+        <v>403</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8543,7 +8747,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>89</v>
@@ -8558,17 +8762,17 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>182</v>
+        <v>109</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>343</v>
+        <v>404</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>344</v>
+        <v>405</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>345</v>
+        <v>406</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>19</v>
@@ -8593,11 +8797,13 @@
         <v>19</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y57" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z57" t="s" s="2">
-        <v>367</v>
+        <v>19</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>19</v>
@@ -8615,16 +8821,16 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>342</v>
+        <v>407</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>19</v>
+        <v>408</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>101</v>
@@ -8636,7 +8842,7 @@
         <v>19</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>19</v>
+        <v>409</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>19</v>
@@ -8645,15 +8851,15 @@
         <v>19</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>19</v>
+        <v>410</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>368</v>
+        <v>411</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8661,7 +8867,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>89</v>
@@ -8676,19 +8882,17 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>149</v>
+        <v>211</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>349</v>
+        <v>413</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>351</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>352</v>
+        <v>415</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>19</v>
@@ -8737,16 +8941,16 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>348</v>
+        <v>416</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>19</v>
+        <v>408</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>101</v>
@@ -8758,24 +8962,24 @@
         <v>19</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>19</v>
+        <v>417</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>353</v>
+        <v>19</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>354</v>
+        <v>19</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>355</v>
+        <v>418</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>369</v>
+        <v>419</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>356</v>
+        <v>420</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8798,17 +9002,19 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>203</v>
+        <v>421</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>357</v>
+        <v>422</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="O59" t="s" s="2">
-        <v>359</v>
+        <v>425</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>19</v>
@@ -8857,7 +9063,7 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>356</v>
+        <v>426</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8878,24 +9084,24 @@
         <v>19</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>19</v>
+        <v>427</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>353</v>
+        <v>19</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>354</v>
+        <v>19</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>360</v>
+        <v>428</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>370</v>
+        <v>429</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>370</v>
+        <v>430</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8918,17 +9124,19 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>371</v>
+        <v>211</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>372</v>
+        <v>431</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="O60" t="s" s="2">
-        <v>374</v>
+        <v>434</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>19</v>
@@ -8977,7 +9185,7 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>370</v>
+        <v>435</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8998,7 +9206,7 @@
         <v>19</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>19</v>
+        <v>436</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>19</v>
@@ -9007,15 +9215,15 @@
         <v>19</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>19</v>
+        <v>437</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>375</v>
+        <v>438</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>375</v>
+        <v>347</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9023,7 +9231,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>89</v>
@@ -9038,17 +9246,19 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>203</v>
+        <v>149</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>376</v>
+        <v>348</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="O61" t="s" s="2">
-        <v>378</v>
+        <v>351</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>19</v>
@@ -9097,10 +9307,10 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>375</v>
+        <v>347</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>89</v>
@@ -9121,32 +9331,32 @@
         <v>19</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>379</v>
+        <v>352</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>19</v>
+        <v>353</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>19</v>
+        <v>354</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>380</v>
+        <v>439</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>381</v>
+        <v>19</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>19</v>
@@ -9155,22 +9365,20 @@
         <v>19</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>382</v>
+        <v>356</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>385</v>
+        <v>358</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>19</v>
@@ -9219,13 +9427,13 @@
         <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>19</v>
@@ -9243,21 +9451,21 @@
         <v>19</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>19</v>
+        <v>352</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>19</v>
+        <v>353</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>19</v>
+        <v>359</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>386</v>
+        <v>440</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>386</v>
+        <v>440</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9277,19 +9485,21 @@
         <v>19</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>203</v>
+        <v>441</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>162</v>
+        <v>442</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>163</v>
+        <v>443</v>
       </c>
       <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>19</v>
       </c>
@@ -9337,7 +9547,7 @@
         <v>19</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>164</v>
+        <v>440</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9346,10 +9556,10 @@
         <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>165</v>
+        <v>19</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>19</v>
@@ -9358,7 +9568,7 @@
         <v>19</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>166</v>
+        <v>19</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>19</v>
@@ -9372,21 +9582,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>387</v>
+        <v>445</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>387</v>
+        <v>445</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>19</v>
@@ -9395,21 +9605,21 @@
         <v>19</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>138</v>
+        <v>446</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>19</v>
       </c>
@@ -9457,19 +9667,19 @@
         <v>19</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>171</v>
+        <v>445</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>19</v>
@@ -9478,10 +9688,10 @@
         <v>19</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>166</v>
+        <v>19</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>19</v>
+        <v>449</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>19</v>
@@ -9492,14 +9702,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>388</v>
+        <v>450</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>388</v>
+        <v>450</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>260</v>
+        <v>451</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9512,25 +9722,25 @@
         <v>19</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>137</v>
+        <v>253</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>261</v>
+        <v>452</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>262</v>
+        <v>453</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>140</v>
+        <v>454</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>146</v>
+        <v>455</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>19</v>
@@ -9579,7 +9789,7 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>263</v>
+        <v>450</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9591,7 +9801,7 @@
         <v>19</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>19</v>
@@ -9600,7 +9810,7 @@
         <v>19</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>19</v>
@@ -9614,10 +9824,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>389</v>
+        <v>456</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>389</v>
+        <v>456</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9637,23 +9847,19 @@
         <v>19</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>390</v>
+        <v>165</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>19</v>
       </c>
@@ -9677,13 +9883,13 @@
         <v>19</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>187</v>
+        <v>19</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>394</v>
+        <v>19</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>395</v>
+        <v>19</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>19</v>
@@ -9701,7 +9907,7 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>389</v>
+        <v>167</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9710,10 +9916,10 @@
         <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>19</v>
@@ -9722,7 +9928,7 @@
         <v>19</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>19</v>
@@ -9736,21 +9942,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>396</v>
+        <v>457</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>396</v>
+        <v>457</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>19</v>
+        <v>136</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>19</v>
@@ -9762,20 +9968,18 @@
         <v>19</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>397</v>
+        <v>138</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>398</v>
+        <v>172</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>19</v>
       </c>
@@ -9799,11 +10003,13 @@
         <v>19</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="Y67" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z67" t="s" s="2">
-        <v>402</v>
+        <v>19</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>19</v>
@@ -9821,19 +10027,19 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>396</v>
+        <v>175</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>19</v>
@@ -9842,7 +10048,7 @@
         <v>19</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>19</v>
@@ -9856,43 +10062,45 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>403</v>
+        <v>458</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>403</v>
+        <v>458</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>19</v>
+        <v>259</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>404</v>
+        <v>260</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O68" t="s" s="2">
-        <v>406</v>
+        <v>146</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>19</v>
@@ -9917,11 +10125,13 @@
         <v>19</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="Y68" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z68" t="s" s="2">
-        <v>407</v>
+        <v>19</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>19</v>
@@ -9939,19 +10149,19 @@
         <v>19</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>403</v>
+        <v>262</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>19</v>
@@ -9960,7 +10170,7 @@
         <v>19</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>19</v>
@@ -9974,10 +10184,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>408</v>
+        <v>459</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>408</v>
+        <v>459</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9997,20 +10207,22 @@
         <v>19</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>409</v>
+        <v>460</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="O69" t="s" s="2">
-        <v>411</v>
+        <v>463</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>19</v>
@@ -10035,11 +10247,13 @@
         <v>19</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="Y69" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="Z69" t="s" s="2">
-        <v>412</v>
+        <v>465</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>19</v>
@@ -10057,7 +10271,7 @@
         <v>19</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>408</v>
+        <v>459</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10092,10 +10306,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>413</v>
+        <v>466</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>413</v>
+        <v>466</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10118,17 +10332,19 @@
         <v>19</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>414</v>
+        <v>467</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="O70" t="s" s="2">
-        <v>411</v>
+        <v>470</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>19</v>
@@ -10153,11 +10369,11 @@
         <v>19</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>401</v>
+        <v>471</v>
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>416</v>
+        <v>472</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>19</v>
@@ -10175,7 +10391,7 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>413</v>
+        <v>466</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10210,10 +10426,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10233,22 +10449,20 @@
         <v>19</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>418</v>
+        <v>188</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>419</v>
+        <v>474</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>422</v>
+        <v>476</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>19</v>
@@ -10273,13 +10487,11 @@
         <v>19</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>19</v>
+        <v>477</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>19</v>
@@ -10297,7 +10509,7 @@
         <v>19</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10321,21 +10533,21 @@
         <v>19</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>353</v>
+        <v>19</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>354</v>
+        <v>19</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>360</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>423</v>
+        <v>478</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>423</v>
+        <v>478</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10346,7 +10558,7 @@
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>19</v>
@@ -10358,17 +10570,17 @@
         <v>19</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>254</v>
+        <v>188</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>424</v>
+        <v>479</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>425</v>
+        <v>480</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>385</v>
+        <v>481</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>19</v>
@@ -10393,13 +10605,11 @@
         <v>19</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>19</v>
+        <v>482</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>19</v>
@@ -10417,13 +10627,13 @@
         <v>19</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>423</v>
+        <v>478</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>19</v>
@@ -10452,10 +10662,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>426</v>
+        <v>483</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>426</v>
+        <v>483</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10478,16 +10688,18 @@
         <v>19</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>162</v>
+        <v>484</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>163</v>
+        <v>485</v>
       </c>
       <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+      <c r="O73" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>19</v>
       </c>
@@ -10511,13 +10723,11 @@
         <v>19</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>19</v>
+        <v>486</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>19</v>
@@ -10535,7 +10745,7 @@
         <v>19</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>164</v>
+        <v>483</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10544,10 +10754,10 @@
         <v>89</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>165</v>
+        <v>19</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>19</v>
@@ -10556,7 +10766,7 @@
         <v>19</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>166</v>
+        <v>19</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>19</v>
@@ -10570,21 +10780,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>427</v>
+        <v>487</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>427</v>
+        <v>487</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>19</v>
@@ -10593,21 +10803,23 @@
         <v>19</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>137</v>
+        <v>488</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>138</v>
+        <v>489</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>168</v>
+        <v>490</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>19</v>
       </c>
@@ -10655,19 +10867,19 @@
         <v>19</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>171</v>
+        <v>487</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>19</v>
@@ -10676,28 +10888,28 @@
         <v>19</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>166</v>
+        <v>19</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>19</v>
+        <v>352</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>19</v>
+        <v>353</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>19</v>
+        <v>359</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>428</v>
+        <v>493</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>428</v>
+        <v>493</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>260</v>
+        <v>19</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10710,25 +10922,23 @@
         <v>19</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>137</v>
+        <v>253</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>261</v>
+        <v>494</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>146</v>
+        <v>455</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>19</v>
@@ -10777,7 +10987,7 @@
         <v>19</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>263</v>
+        <v>493</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10789,7 +10999,7 @@
         <v>19</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>19</v>
@@ -10798,7 +11008,7 @@
         <v>19</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>19</v>
@@ -10812,10 +11022,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>429</v>
+        <v>496</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>429</v>
+        <v>496</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10823,7 +11033,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>89</v>
@@ -10835,21 +11045,19 @@
         <v>19</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>430</v>
+        <v>165</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>431</v>
+        <v>166</v>
       </c>
       <c r="N76" s="2"/>
-      <c r="O76" t="s" s="2">
-        <v>432</v>
-      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>19</v>
       </c>
@@ -10873,13 +11081,13 @@
         <v>19</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>401</v>
+        <v>19</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>433</v>
+        <v>19</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>434</v>
+        <v>19</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>19</v>
@@ -10897,19 +11105,19 @@
         <v>19</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>429</v>
+        <v>167</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>19</v>
@@ -10918,7 +11126,7 @@
         <v>19</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>19</v>
@@ -10932,21 +11140,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>435</v>
+        <v>497</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>435</v>
+        <v>497</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>19</v>
+        <v>136</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>19</v>
@@ -10955,21 +11163,21 @@
         <v>19</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>213</v>
+        <v>137</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>436</v>
+        <v>138</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>19</v>
       </c>
@@ -11017,19 +11225,19 @@
         <v>19</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>435</v>
+        <v>175</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>19</v>
@@ -11038,7 +11246,7 @@
         <v>19</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>19</v>
@@ -11052,45 +11260,45 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>439</v>
+        <v>498</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>439</v>
+        <v>498</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>19</v>
+        <v>259</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>440</v>
+        <v>137</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>441</v>
+        <v>260</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>442</v>
+        <v>261</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>443</v>
+        <v>140</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>444</v>
+        <v>146</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>19</v>
@@ -11139,19 +11347,19 @@
         <v>19</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>439</v>
+        <v>262</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>19</v>
@@ -11160,7 +11368,7 @@
         <v>19</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>19</v>
@@ -11174,10 +11382,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>445</v>
+        <v>499</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>445</v>
+        <v>499</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11185,10 +11393,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>19</v>
@@ -11197,20 +11405,20 @@
         <v>19</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>446</v>
+        <v>188</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>447</v>
+        <v>500</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>448</v>
+        <v>501</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>449</v>
+        <v>502</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>19</v>
@@ -11235,13 +11443,13 @@
         <v>19</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>19</v>
+        <v>471</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>19</v>
+        <v>503</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>19</v>
+        <v>504</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>19</v>
@@ -11259,13 +11467,13 @@
         <v>19</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>445</v>
+        <v>499</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>19</v>
@@ -11280,24 +11488,24 @@
         <v>19</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>166</v>
+        <v>19</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>286</v>
+        <v>19</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>287</v>
+        <v>19</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>450</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>451</v>
+        <v>505</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>451</v>
+        <v>505</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11317,20 +11525,20 @@
         <v>19</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>452</v>
+        <v>222</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>453</v>
+        <v>506</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>454</v>
+        <v>507</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>455</v>
+        <v>508</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>19</v>
@@ -11379,7 +11587,7 @@
         <v>19</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>451</v>
+        <v>505</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11412,8 +11620,370 @@
         <v>19</v>
       </c>
     </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="P81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP81" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AP82" t="s" s="2">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP83" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AP80">
+  <autoFilter ref="A1:AP83">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11423,7 +11993,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI79">
+  <conditionalFormatting sqref="A2:AI82">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:00:23+00:00</t>
+    <t>2024-11-12T19:16:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:16:24+00:00</t>
+    <t>2024-11-12T19:22:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:22:29+00:00</t>
+    <t>2024-11-14T14:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:59:39+00:00</t>
+    <t>2024-11-14T15:15:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T15:15:53+00:00</t>
+    <t>2024-11-15T07:51:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T07:51:28+00:00</t>
+    <t>2024-11-15T09:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T09:58:51+00:00</t>
+    <t>2024-11-15T11:02:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T11:02:30+00:00</t>
+    <t>2024-11-15T19:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:27:47+00:00</t>
+    <t>2024-11-15T20:19:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T20:19:59+00:00</t>
+    <t>2024-11-17T19:53:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T19:53:01+00:00</t>
+    <t>2024-11-17T20:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T20:11:24+00:00</t>
+    <t>2024-11-20T22:25:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-20T22:25:32+00:00</t>
+    <t>2024-11-22T08:03:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-22T08:03:54+00:00</t>
+    <t>2024-12-12T14:30:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-13T08:39:47+00:00</t>
+    <t>2025-01-07T14:12:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:12:01+00:00</t>
+    <t>2025-01-07T14:17:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:17:45+00:00</t>
+    <t>2025-01-14T08:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:01:21+00:00</t>
+    <t>2025-01-14T08:16:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3346,7 +3346,7 @@
         <v>90</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>20</v>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:16:01+00:00</t>
+    <t>2025-02-07T07:07:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T07:07:15+00:00</t>
+    <t>2025-02-07T10:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T10:07:52+00:00</t>
+    <t>2025-02-10T08:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:30:06+00:00</t>
+    <t>2025-02-10T08:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:38:31+00:00</t>
+    <t>2025-02-11T11:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:17:52+00:00</t>
+    <t>2025-02-11T16:50:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
